--- a/NJSBCL/data/weekenderscup_schedule.xlsx
+++ b/NJSBCL/data/weekenderscup_schedule.xlsx
@@ -323,7 +323,7 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F3">
@@ -333,22 +333,22 @@
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -368,7 +368,7 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F4">
@@ -378,22 +378,22 @@
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Tridents XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F5">
@@ -423,22 +423,22 @@
       </c>
       <c t="inlineStr" r="G5">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -458,7 +458,7 @@
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F6">
@@ -468,22 +468,22 @@
       </c>
       <c t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I6">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F7">
@@ -513,22 +513,22 @@
       </c>
       <c t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
@@ -558,22 +558,22 @@
       </c>
       <c t="inlineStr" r="G8">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F9">
@@ -603,22 +603,17 @@
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J9">
-        <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -638,7 +633,7 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
@@ -648,22 +643,22 @@
       </c>
       <c t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -683,7 +678,7 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F11">
@@ -693,22 +688,17 @@
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J11">
-        <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -728,32 +718,27 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G12">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J12">
-        <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
     </row>
@@ -773,7 +758,7 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
@@ -783,22 +768,22 @@
       </c>
       <c t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -818,7 +803,7 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
@@ -828,22 +813,22 @@
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -863,7 +848,7 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F15">
@@ -873,22 +858,22 @@
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -908,7 +893,7 @@
       </c>
       <c t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F16">
@@ -918,22 +903,22 @@
       </c>
       <c t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -953,7 +938,7 @@
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F17">
@@ -963,22 +948,22 @@
       </c>
       <c t="inlineStr" r="G17">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I17">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -998,7 +983,7 @@
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F18">
@@ -1008,22 +993,22 @@
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I18">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1028,7 @@
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
@@ -1053,22 +1038,22 @@
       </c>
       <c t="inlineStr" r="G19">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1073,7 @@
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F20">
@@ -1098,22 +1083,22 @@
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1118,7 @@
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F21">
@@ -1143,22 +1128,17 @@
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J21">
-        <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1158,7 @@
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">08/15/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F22">
@@ -1188,22 +1168,22 @@
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1203,7 @@
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
@@ -1238,17 +1218,17 @@
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1248,7 @@
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
@@ -1283,17 +1263,17 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">Tridents XI</t>
+          <t xml:space="preserve">PMCC</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1293,7 @@
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
@@ -1328,17 +1308,17 @@
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1338,7 @@
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
@@ -1373,17 +1353,17 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1383,7 @@
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
@@ -1418,17 +1398,17 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1428,7 @@
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
@@ -1463,17 +1443,17 @@
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="J28">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1473,7 @@
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
@@ -1508,17 +1488,17 @@
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J29">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1518,7 @@
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
@@ -1553,17 +1533,17 @@
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="J30">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1563,7 @@
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
@@ -1598,17 +1578,17 @@
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I31">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="J31">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1608,12 @@
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
@@ -1643,17 +1623,17 @@
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="J32">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1653,7 @@
       </c>
       <c t="inlineStr" r="E33">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F33">
@@ -1688,17 +1668,17 @@
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t xml:space="preserve">NJ Warriors</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="J33">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1698,7 @@
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
@@ -1733,17 +1713,17 @@
       </c>
       <c t="inlineStr" r="H34">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I34">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J34">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1743,7 @@
       </c>
       <c t="inlineStr" r="E35">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F35">
@@ -1778,17 +1758,17 @@
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I35">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="J35">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1788,7 @@
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
@@ -1823,17 +1803,17 @@
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I36">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="J36">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1833,7 @@
       </c>
       <c t="inlineStr" r="E37">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F37">
@@ -1868,17 +1848,17 @@
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I37">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J37">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1878,7 @@
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
@@ -1913,17 +1893,17 @@
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="J38">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1923,7 @@
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
@@ -1958,17 +1938,17 @@
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="J39">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1968,7 @@
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
@@ -2003,17 +1983,17 @@
       </c>
       <c t="inlineStr" r="H40">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I40">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="J40">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2013,7 @@
       </c>
       <c t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F41">
@@ -2048,17 +2028,17 @@
       </c>
       <c t="inlineStr" r="H41">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I41">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="J41">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2058,7 @@
       </c>
       <c t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F42">
@@ -2093,17 +2073,17 @@
       </c>
       <c t="inlineStr" r="H42">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I42">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="J42">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2103,7 @@
       </c>
       <c t="inlineStr" r="E43">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F43">
@@ -2133,22 +2113,22 @@
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2148,7 @@
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
@@ -2178,22 +2158,22 @@
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I44">
         <is>
-          <t xml:space="preserve">PMCC</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="J44">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2193,7 @@
       </c>
       <c t="inlineStr" r="E45">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F45">
@@ -2223,22 +2203,22 @@
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="J45">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2238,7 @@
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
@@ -2268,22 +2248,22 @@
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2283,7 @@
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
@@ -2313,22 +2293,22 @@
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I47">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Bloodline</t>
         </is>
       </c>
       <c t="inlineStr" r="J47">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2328,7 @@
       </c>
       <c t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F48">
@@ -2358,22 +2338,22 @@
       </c>
       <c t="inlineStr" r="G48">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H48">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I48">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J48">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2373,7 @@
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
@@ -2403,22 +2383,22 @@
       </c>
       <c t="inlineStr" r="G49">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="J49">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2418,7 @@
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
@@ -2448,22 +2428,22 @@
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="J50">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2463,7 @@
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
@@ -2493,22 +2473,22 @@
       </c>
       <c t="inlineStr" r="G51">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">JC Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J51">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2508,7 @@
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
@@ -2538,22 +2518,22 @@
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Champions</t>
         </is>
       </c>
       <c t="inlineStr" r="J52">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2553,7 @@
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
@@ -2583,22 +2563,22 @@
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I53">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="J53">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2598,7 @@
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
@@ -2628,22 +2608,22 @@
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J54">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2643,7 @@
       </c>
       <c t="inlineStr" r="E55">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F55">
@@ -2673,22 +2653,22 @@
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="J55">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2688,7 @@
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
@@ -2718,22 +2698,22 @@
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="J56">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2733,7 @@
       </c>
       <c t="inlineStr" r="E57">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F57">
@@ -2763,22 +2743,22 @@
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J57">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2778,7 @@
       </c>
       <c t="inlineStr" r="E58">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F58">
@@ -2808,22 +2788,22 @@
       </c>
       <c t="inlineStr" r="G58">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H58">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="J58">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2823,7 @@
       </c>
       <c t="inlineStr" r="E59">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F59">
@@ -2853,22 +2833,22 @@
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J59">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2868,7 @@
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
@@ -2898,22 +2878,22 @@
       </c>
       <c t="inlineStr" r="G60">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J60">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2913,7 @@
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
@@ -2943,22 +2923,22 @@
       </c>
       <c t="inlineStr" r="G61">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Jersey Tigers</t>
         </is>
       </c>
       <c t="inlineStr" r="J61">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2958,7 @@
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
@@ -2988,22 +2968,22 @@
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J62">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3003,7 @@
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
@@ -3038,17 +3018,17 @@
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J63">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3048,7 @@
       </c>
       <c t="inlineStr" r="E64">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F64">
@@ -3083,17 +3063,17 @@
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J64">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3093,7 @@
       </c>
       <c t="inlineStr" r="E65">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F65">
@@ -3128,17 +3108,17 @@
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="J65">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3138,7 @@
       </c>
       <c t="inlineStr" r="E66">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F66">
@@ -3173,17 +3153,17 @@
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J66">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3183,7 @@
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
@@ -3218,17 +3198,17 @@
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t xml:space="preserve">Bloodline</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="J67">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3228,7 @@
       </c>
       <c t="inlineStr" r="E68">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F68">
@@ -3263,17 +3243,17 @@
       </c>
       <c t="inlineStr" r="H68">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I68">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J68">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3273,7 @@
       </c>
       <c t="inlineStr" r="E69">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F69">
@@ -3308,17 +3288,17 @@
       </c>
       <c t="inlineStr" r="H69">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J69">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3318,7 @@
       </c>
       <c t="inlineStr" r="E70">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F70">
@@ -3353,17 +3333,17 @@
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="J70">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3363,7 @@
       </c>
       <c t="inlineStr" r="E71">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F71">
@@ -3398,17 +3378,17 @@
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t xml:space="preserve">JC Mavericks</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="J71">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3408,7 @@
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
@@ -3443,17 +3423,17 @@
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t xml:space="preserve">Champions</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J72">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3453,7 @@
       </c>
       <c t="inlineStr" r="E73">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F73">
@@ -3488,17 +3468,17 @@
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="J73">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3498,7 @@
       </c>
       <c t="inlineStr" r="E74">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F74">
@@ -3533,17 +3513,17 @@
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="J74">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3543,7 @@
       </c>
       <c t="inlineStr" r="E75">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F75">
@@ -3578,17 +3558,17 @@
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="J75">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3588,7 @@
       </c>
       <c t="inlineStr" r="E76">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F76">
@@ -3623,17 +3603,17 @@
       </c>
       <c t="inlineStr" r="H76">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I76">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J76">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3633,7 @@
       </c>
       <c t="inlineStr" r="E77">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F77">
@@ -3668,17 +3648,17 @@
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I77">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J77">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3678,7 @@
       </c>
       <c t="inlineStr" r="E78">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F78">
@@ -3713,17 +3693,17 @@
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I78">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">EM Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J78">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3723,7 @@
       </c>
       <c t="inlineStr" r="E79">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F79">
@@ -3758,17 +3738,17 @@
       </c>
       <c t="inlineStr" r="H79">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I79">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J79">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3768,7 @@
       </c>
       <c t="inlineStr" r="E80">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F80">
@@ -3803,17 +3783,17 @@
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I80">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J80">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3813,7 @@
       </c>
       <c t="inlineStr" r="E81">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F81">
@@ -3848,17 +3828,17 @@
       </c>
       <c t="inlineStr" r="H81">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I81">
         <is>
-          <t xml:space="preserve">Jersey Tigers</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J81">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3858,7 @@
       </c>
       <c t="inlineStr" r="E82">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F82">
@@ -3893,17 +3873,17 @@
       </c>
       <c t="inlineStr" r="H82">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I82">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="J82">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3903,7 @@
       </c>
       <c t="inlineStr" r="E83">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F83">
@@ -3933,22 +3913,22 @@
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I83">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J83">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3948,7 @@
       </c>
       <c t="inlineStr" r="E84">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F84">
@@ -3978,22 +3958,22 @@
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I84">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J84">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -4013,7 +3993,7 @@
       </c>
       <c t="inlineStr" r="E85">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F85">
@@ -4023,22 +4003,22 @@
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I85">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J85">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4038,7 @@
       </c>
       <c t="inlineStr" r="E86">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F86">
@@ -4068,22 +4048,22 @@
       </c>
       <c t="inlineStr" r="G86">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I86">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J86">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4083,7 @@
       </c>
       <c t="inlineStr" r="E87">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F87">
@@ -4113,22 +4093,22 @@
       </c>
       <c t="inlineStr" r="G87">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H87">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I87">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J87">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4128,7 @@
       </c>
       <c t="inlineStr" r="E88">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F88">
@@ -4158,22 +4138,22 @@
       </c>
       <c t="inlineStr" r="G88">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H88">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I88">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J88">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4173,7 @@
       </c>
       <c t="inlineStr" r="E89">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F89">
@@ -4203,22 +4183,22 @@
       </c>
       <c t="inlineStr" r="G89">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H89">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I89">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="J89">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4218,7 @@
       </c>
       <c t="inlineStr" r="E90">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F90">
@@ -4248,22 +4228,22 @@
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I90">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J90">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4263,32 @@
       </c>
       <c t="inlineStr" r="E91">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G91">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H91">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I91">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
       <c t="inlineStr" r="J91">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4308,7 @@
       </c>
       <c t="inlineStr" r="E92">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F92">
@@ -4338,22 +4318,22 @@
       </c>
       <c t="inlineStr" r="G92">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H92">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I92">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Tridents XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J92">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4353,7 @@
       </c>
       <c t="inlineStr" r="E93">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F93">
@@ -4383,22 +4363,22 @@
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I93">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J93">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4398,7 @@
       </c>
       <c t="inlineStr" r="E94">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F94">
@@ -4428,22 +4408,22 @@
       </c>
       <c t="inlineStr" r="G94">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H94">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I94">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J94">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4443,7 @@
       </c>
       <c t="inlineStr" r="E95">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F95">
@@ -4473,22 +4453,22 @@
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I95">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J95">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4488,7 @@
       </c>
       <c t="inlineStr" r="E96">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F96">
@@ -4518,22 +4498,22 @@
       </c>
       <c t="inlineStr" r="G96">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H96">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I96">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J96">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4533,7 @@
       </c>
       <c t="inlineStr" r="E97">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F97">
@@ -4563,22 +4543,22 @@
       </c>
       <c t="inlineStr" r="G97">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H97">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I97">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J97">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4578,7 @@
       </c>
       <c t="inlineStr" r="E98">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F98">
@@ -4608,22 +4588,22 @@
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I98">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J98">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4623,7 @@
       </c>
       <c t="inlineStr" r="E99">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F99">
@@ -4653,22 +4633,22 @@
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I99">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J99">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4668,7 @@
       </c>
       <c t="inlineStr" r="E100">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F100">
@@ -4698,22 +4678,22 @@
       </c>
       <c t="inlineStr" r="G100">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H100">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I100">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J100">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4713,7 @@
       </c>
       <c t="inlineStr" r="E101">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F101">
@@ -4743,22 +4723,22 @@
       </c>
       <c t="inlineStr" r="G101">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H101">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I101">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J101">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4758,7 @@
       </c>
       <c t="inlineStr" r="E102">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F102">
@@ -4788,22 +4768,22 @@
       </c>
       <c t="inlineStr" r="G102">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H102">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I102">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J102">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4803,7 @@
       </c>
       <c t="inlineStr" r="E103">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F103">
@@ -4838,17 +4818,17 @@
       </c>
       <c t="inlineStr" r="H103">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I103">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J103">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4848,7 @@
       </c>
       <c t="inlineStr" r="E104">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F104">
@@ -4883,17 +4863,17 @@
       </c>
       <c t="inlineStr" r="H104">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I104">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">PMCC</t>
         </is>
       </c>
       <c t="inlineStr" r="J104">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4893,7 @@
       </c>
       <c t="inlineStr" r="E105">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F105">
@@ -4928,17 +4908,17 @@
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I105">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="J105">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4938,7 @@
       </c>
       <c t="inlineStr" r="E106">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F106">
@@ -4973,17 +4953,17 @@
       </c>
       <c t="inlineStr" r="H106">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I106">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J106">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
     </row>
@@ -5003,7 +4983,7 @@
       </c>
       <c t="inlineStr" r="E107">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F107">
@@ -5018,17 +4998,17 @@
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I107">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J107">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5028,7 @@
       </c>
       <c t="inlineStr" r="E108">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F108">
@@ -5063,17 +5043,17 @@
       </c>
       <c t="inlineStr" r="H108">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I108">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="J108">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5073,7 @@
       </c>
       <c t="inlineStr" r="E109">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F109">
@@ -5108,17 +5088,17 @@
       </c>
       <c t="inlineStr" r="H109">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I109">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J109">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5118,7 @@
       </c>
       <c t="inlineStr" r="E110">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F110">
@@ -5153,17 +5133,17 @@
       </c>
       <c t="inlineStr" r="H110">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I110">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="J110">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5163,12 @@
       </c>
       <c t="inlineStr" r="E111">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G111">
@@ -5198,17 +5178,17 @@
       </c>
       <c t="inlineStr" r="H111">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I111">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="J111">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5208,7 @@
       </c>
       <c t="inlineStr" r="E112">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F112">
@@ -5243,17 +5223,17 @@
       </c>
       <c t="inlineStr" r="H112">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I112">
         <is>
-          <t xml:space="preserve">Tridents XI</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="J112">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5253,7 @@
       </c>
       <c t="inlineStr" r="E113">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F113">
@@ -5288,17 +5268,17 @@
       </c>
       <c t="inlineStr" r="H113">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I113">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="J113">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5298,7 @@
       </c>
       <c t="inlineStr" r="E114">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F114">
@@ -5333,17 +5313,17 @@
       </c>
       <c t="inlineStr" r="H114">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I114">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J114">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5343,7 @@
       </c>
       <c t="inlineStr" r="E115">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F115">
@@ -5378,17 +5358,17 @@
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I115">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="J115">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5388,7 @@
       </c>
       <c t="inlineStr" r="E116">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F116">
@@ -5423,17 +5403,17 @@
       </c>
       <c t="inlineStr" r="H116">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I116">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="J116">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5433,7 @@
       </c>
       <c t="inlineStr" r="E117">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F117">
@@ -5468,17 +5448,17 @@
       </c>
       <c t="inlineStr" r="H117">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I117">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J117">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5478,7 @@
       </c>
       <c t="inlineStr" r="E118">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F118">
@@ -5513,17 +5493,17 @@
       </c>
       <c t="inlineStr" r="H118">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I118">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="J118">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5523,7 @@
       </c>
       <c t="inlineStr" r="E119">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F119">
@@ -5558,17 +5538,17 @@
       </c>
       <c t="inlineStr" r="H119">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I119">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="J119">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5568,7 @@
       </c>
       <c t="inlineStr" r="E120">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F120">
@@ -5603,17 +5583,17 @@
       </c>
       <c t="inlineStr" r="H120">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I120">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="J120">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5613,7 @@
       </c>
       <c t="inlineStr" r="E121">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F121">
@@ -5648,17 +5628,17 @@
       </c>
       <c t="inlineStr" r="H121">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I121">
         <is>
-          <t xml:space="preserve">NJ Warriors</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="J121">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5658,7 @@
       </c>
       <c t="inlineStr" r="E122">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F122">
@@ -5693,17 +5673,17 @@
       </c>
       <c t="inlineStr" r="H122">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I122">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="J122">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5703,7 @@
       </c>
       <c t="inlineStr" r="E123">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F123">
@@ -5733,22 +5713,22 @@
       </c>
       <c t="inlineStr" r="G123">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H123">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I123">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="J123">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5748,7 @@
       </c>
       <c t="inlineStr" r="E124">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F124">
@@ -5778,22 +5758,22 @@
       </c>
       <c t="inlineStr" r="G124">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H124">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I124">
         <is>
-          <t xml:space="preserve">PMCC</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J124">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5793,7 @@
       </c>
       <c t="inlineStr" r="E125">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F125">
@@ -5823,22 +5803,22 @@
       </c>
       <c t="inlineStr" r="G125">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H125">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I125">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Bloodline</t>
         </is>
       </c>
       <c t="inlineStr" r="J125">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5838,7 @@
       </c>
       <c t="inlineStr" r="E126">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F126">
@@ -5868,22 +5848,22 @@
       </c>
       <c t="inlineStr" r="G126">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H126">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I126">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J126">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5883,7 @@
       </c>
       <c t="inlineStr" r="E127">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F127">
@@ -5913,22 +5893,22 @@
       </c>
       <c t="inlineStr" r="G127">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H127">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I127">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="J127">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5928,7 @@
       </c>
       <c t="inlineStr" r="E128">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F128">
@@ -5958,22 +5938,22 @@
       </c>
       <c t="inlineStr" r="G128">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H128">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I128">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="J128">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5973,7 @@
       </c>
       <c t="inlineStr" r="E129">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F129">
@@ -6003,22 +5983,22 @@
       </c>
       <c t="inlineStr" r="G129">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H129">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I129">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">JC Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J129">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6018,7 @@
       </c>
       <c t="inlineStr" r="E130">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F130">
@@ -6048,22 +6028,22 @@
       </c>
       <c t="inlineStr" r="G130">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H130">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I130">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Champions</t>
         </is>
       </c>
       <c t="inlineStr" r="J130">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6063,7 @@
       </c>
       <c t="inlineStr" r="E131">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F131">
@@ -6093,22 +6073,22 @@
       </c>
       <c t="inlineStr" r="G131">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H131">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I131">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J131">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6108,7 @@
       </c>
       <c t="inlineStr" r="E132">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F132">
@@ -6138,22 +6118,22 @@
       </c>
       <c t="inlineStr" r="G132">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H132">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I132">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="J132">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6153,7 @@
       </c>
       <c t="inlineStr" r="E133">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F133">
@@ -6183,22 +6163,22 @@
       </c>
       <c t="inlineStr" r="G133">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H133">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I133">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="J133">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6198,7 @@
       </c>
       <c t="inlineStr" r="E134">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F134">
@@ -6228,22 +6208,22 @@
       </c>
       <c t="inlineStr" r="G134">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H134">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I134">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="J134">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6243,7 @@
       </c>
       <c t="inlineStr" r="E135">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F135">
@@ -6273,22 +6253,22 @@
       </c>
       <c t="inlineStr" r="G135">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H135">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I135">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J135">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6288,7 @@
       </c>
       <c t="inlineStr" r="E136">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F136">
@@ -6318,22 +6298,22 @@
       </c>
       <c t="inlineStr" r="G136">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H136">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I136">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="J136">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6333,7 @@
       </c>
       <c t="inlineStr" r="E137">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F137">
@@ -6363,22 +6343,22 @@
       </c>
       <c t="inlineStr" r="G137">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H137">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I137">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J137">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6378,7 @@
       </c>
       <c t="inlineStr" r="E138">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F138">
@@ -6408,22 +6388,22 @@
       </c>
       <c t="inlineStr" r="G138">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H138">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I138">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J138">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6423,7 @@
       </c>
       <c t="inlineStr" r="E139">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F139">
@@ -6453,22 +6433,22 @@
       </c>
       <c t="inlineStr" r="G139">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H139">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I139">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J139">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6468,7 @@
       </c>
       <c t="inlineStr" r="E140">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F140">
@@ -6498,22 +6478,22 @@
       </c>
       <c t="inlineStr" r="G140">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H140">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I140">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Jersey Tigers</t>
         </is>
       </c>
       <c t="inlineStr" r="J140">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6513,7 @@
       </c>
       <c t="inlineStr" r="E141">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F141">
@@ -6543,22 +6523,22 @@
       </c>
       <c t="inlineStr" r="G141">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H141">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I141">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J141">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6558,7 @@
       </c>
       <c t="inlineStr" r="E142">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F142">
@@ -6588,22 +6568,22 @@
       </c>
       <c t="inlineStr" r="G142">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H142">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I142">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="J142">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6603,7 @@
       </c>
       <c t="inlineStr" r="E143">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F143">
@@ -6638,17 +6618,17 @@
       </c>
       <c t="inlineStr" r="H143">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I143">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J143">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6648,7 @@
       </c>
       <c t="inlineStr" r="E144">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F144">
@@ -6683,17 +6663,17 @@
       </c>
       <c t="inlineStr" r="H144">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I144">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J144">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6693,7 @@
       </c>
       <c t="inlineStr" r="E145">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F145">
@@ -6728,17 +6708,17 @@
       </c>
       <c t="inlineStr" r="H145">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I145">
         <is>
-          <t xml:space="preserve">Bloodline</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="J145">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6738,7 @@
       </c>
       <c t="inlineStr" r="E146">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F146">
@@ -6773,17 +6753,17 @@
       </c>
       <c t="inlineStr" r="H146">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I146">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J146">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6783,7 @@
       </c>
       <c t="inlineStr" r="E147">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F147">
@@ -6818,17 +6798,17 @@
       </c>
       <c t="inlineStr" r="H147">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I147">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="J147">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6828,7 @@
       </c>
       <c t="inlineStr" r="E148">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F148">
@@ -6863,17 +6843,17 @@
       </c>
       <c t="inlineStr" r="H148">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I148">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J148">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6873,7 @@
       </c>
       <c t="inlineStr" r="E149">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F149">
@@ -6908,17 +6888,17 @@
       </c>
       <c t="inlineStr" r="H149">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I149">
         <is>
-          <t xml:space="preserve">JC Mavericks</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J149">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6918,7 @@
       </c>
       <c t="inlineStr" r="E150">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F150">
@@ -6953,17 +6933,17 @@
       </c>
       <c t="inlineStr" r="H150">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I150">
         <is>
-          <t xml:space="preserve">Champions</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="J150">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6963,7 @@
       </c>
       <c t="inlineStr" r="E151">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F151">
@@ -6998,17 +6978,17 @@
       </c>
       <c t="inlineStr" r="H151">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I151">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="J151">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7008,7 @@
       </c>
       <c t="inlineStr" r="E152">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F152">
@@ -7043,17 +7023,17 @@
       </c>
       <c t="inlineStr" r="H152">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I152">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J152">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7053,7 @@
       </c>
       <c t="inlineStr" r="E153">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F153">
@@ -7088,17 +7068,17 @@
       </c>
       <c t="inlineStr" r="H153">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I153">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="J153">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7098,7 @@
       </c>
       <c t="inlineStr" r="E154">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F154">
@@ -7133,17 +7113,17 @@
       </c>
       <c t="inlineStr" r="H154">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I154">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="J154">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7143,7 @@
       </c>
       <c t="inlineStr" r="E155">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F155">
@@ -7178,17 +7158,17 @@
       </c>
       <c t="inlineStr" r="H155">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I155">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="J155">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7188,7 @@
       </c>
       <c t="inlineStr" r="E156">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F156">
@@ -7223,17 +7203,17 @@
       </c>
       <c t="inlineStr" r="H156">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I156">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J156">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7233,7 @@
       </c>
       <c t="inlineStr" r="E157">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F157">
@@ -7268,17 +7248,17 @@
       </c>
       <c t="inlineStr" r="H157">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I157">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J157">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7278,7 @@
       </c>
       <c t="inlineStr" r="E158">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F158">
@@ -7313,17 +7293,17 @@
       </c>
       <c t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I158">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">EM Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J158">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7323,7 @@
       </c>
       <c t="inlineStr" r="E159">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F159">
@@ -7358,17 +7338,17 @@
       </c>
       <c t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I159">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J159">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7368,7 @@
       </c>
       <c t="inlineStr" r="E160">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F160">
@@ -7403,17 +7383,17 @@
       </c>
       <c t="inlineStr" r="H160">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I160">
         <is>
-          <t xml:space="preserve">Jersey Tigers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J160">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7413,7 @@
       </c>
       <c t="inlineStr" r="E161">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F161">
@@ -7448,17 +7428,17 @@
       </c>
       <c t="inlineStr" r="H161">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I161">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J161">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7458,7 @@
       </c>
       <c t="inlineStr" r="E162">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F162">
@@ -7493,17 +7473,17 @@
       </c>
       <c t="inlineStr" r="H162">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I162">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="J162">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7503,7 @@
       </c>
       <c t="inlineStr" r="E163">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F163">
@@ -7533,22 +7513,22 @@
       </c>
       <c t="inlineStr" r="G163">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H163">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I163">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J163">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7548,7 @@
       </c>
       <c t="inlineStr" r="E164">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F164">
@@ -7578,22 +7558,22 @@
       </c>
       <c t="inlineStr" r="G164">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H164">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I164">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J164">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7593,7 @@
       </c>
       <c t="inlineStr" r="E165">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F165">
@@ -7623,22 +7603,22 @@
       </c>
       <c t="inlineStr" r="G165">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H165">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I165">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J165">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7638,7 @@
       </c>
       <c t="inlineStr" r="E166">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F166">
@@ -7668,22 +7648,22 @@
       </c>
       <c t="inlineStr" r="G166">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H166">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I166">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J166">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7683,7 @@
       </c>
       <c t="inlineStr" r="E167">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F167">
@@ -7713,22 +7693,22 @@
       </c>
       <c t="inlineStr" r="G167">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H167">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I167">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="J167">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7728,7 @@
       </c>
       <c t="inlineStr" r="E168">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F168">
@@ -7758,22 +7738,22 @@
       </c>
       <c t="inlineStr" r="G168">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H168">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I168">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J168">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7773,7 @@
       </c>
       <c t="inlineStr" r="E169">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F169">
@@ -7803,22 +7783,22 @@
       </c>
       <c t="inlineStr" r="G169">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H169">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I169">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="J169">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -7838,32 +7818,32 @@
       </c>
       <c t="inlineStr" r="E170">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G170">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H170">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I170">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
       <c t="inlineStr" r="J170">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7863,7 @@
       </c>
       <c t="inlineStr" r="E171">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F171">
@@ -7893,22 +7873,22 @@
       </c>
       <c t="inlineStr" r="G171">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H171">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I171">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J171">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7908,7 @@
       </c>
       <c t="inlineStr" r="E172">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F172">
@@ -7938,22 +7918,22 @@
       </c>
       <c t="inlineStr" r="G172">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H172">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I172">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J172">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7953,7 @@
       </c>
       <c t="inlineStr" r="E173">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F173">
@@ -7983,22 +7963,22 @@
       </c>
       <c t="inlineStr" r="G173">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H173">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I173">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J173">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -8018,7 +7998,7 @@
       </c>
       <c t="inlineStr" r="E174">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F174">
@@ -8028,22 +8008,22 @@
       </c>
       <c t="inlineStr" r="G174">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H174">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I174">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J174">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8043,7 @@
       </c>
       <c t="inlineStr" r="E175">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F175">
@@ -8073,22 +8053,22 @@
       </c>
       <c t="inlineStr" r="G175">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H175">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I175">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J175">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8088,7 @@
       </c>
       <c t="inlineStr" r="E176">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F176">
@@ -8118,22 +8098,22 @@
       </c>
       <c t="inlineStr" r="G176">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H176">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I176">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J176">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8133,7 @@
       </c>
       <c t="inlineStr" r="E177">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F177">
@@ -8163,22 +8143,22 @@
       </c>
       <c t="inlineStr" r="G177">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H177">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I177">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J177">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8178,7 @@
       </c>
       <c t="inlineStr" r="E178">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F178">
@@ -8208,22 +8188,22 @@
       </c>
       <c t="inlineStr" r="G178">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H178">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I178">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J178">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8223,7 @@
       </c>
       <c t="inlineStr" r="E179">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F179">
@@ -8253,22 +8233,22 @@
       </c>
       <c t="inlineStr" r="G179">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H179">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I179">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J179">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8268,7 @@
       </c>
       <c t="inlineStr" r="E180">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F180">
@@ -8298,22 +8278,22 @@
       </c>
       <c t="inlineStr" r="G180">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H180">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I180">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J180">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8313,7 @@
       </c>
       <c t="inlineStr" r="E181">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F181">
@@ -8343,22 +8323,22 @@
       </c>
       <c t="inlineStr" r="G181">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H181">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I181">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J181">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8358,7 @@
       </c>
       <c t="inlineStr" r="E182">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F182">
@@ -8388,22 +8368,22 @@
       </c>
       <c t="inlineStr" r="G182">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H182">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I182">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J182">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8403,7 @@
       </c>
       <c t="inlineStr" r="E183">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F183">
@@ -8433,22 +8413,17 @@
       </c>
       <c t="inlineStr" r="G183">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H183">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I183">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J183">
-        <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8443,7 @@
       </c>
       <c t="inlineStr" r="E184">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F184">
@@ -8478,22 +8453,17 @@
       </c>
       <c t="inlineStr" r="G184">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H184">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I184">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J184">
-        <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8483,7 @@
       </c>
       <c t="inlineStr" r="E185">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F185">
@@ -8523,22 +8493,22 @@
       </c>
       <c t="inlineStr" r="G185">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H185">
         <is>
+          <t xml:space="preserve">Invincible CC</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I185">
+        <is>
+          <t xml:space="preserve">Troy Titans</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J185">
+        <is>
           <t xml:space="preserve">Bayonne CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I185">
-        <is>
-          <t xml:space="preserve">Bayonne CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J185">
-        <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8528,7 @@
       </c>
       <c t="inlineStr" r="E186">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F186">
@@ -8568,22 +8538,22 @@
       </c>
       <c t="inlineStr" r="G186">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H186">
         <is>
+          <t xml:space="preserve">Monroe United</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I186">
+        <is>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J186">
+        <is>
           <t xml:space="preserve">Jersey Sloggers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I186">
-        <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J186">
-        <is>
-          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8573,7 @@
       </c>
       <c t="inlineStr" r="E187">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F187">
@@ -8613,22 +8583,22 @@
       </c>
       <c t="inlineStr" r="G187">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H187">
         <is>
+          <t xml:space="preserve">Iselin Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I187">
+        <is>
+          <t xml:space="preserve">EM Sports Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J187">
+        <is>
           <t xml:space="preserve">Newport Narcos</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I187">
-        <is>
-          <t xml:space="preserve">Newport Narcos</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J187">
-        <is>
-          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8618,7 @@
       </c>
       <c t="inlineStr" r="E188">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F188">
@@ -8658,22 +8628,22 @@
       </c>
       <c t="inlineStr" r="G188">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H188">
         <is>
+          <t xml:space="preserve">NJKnights</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I188">
+        <is>
+          <t xml:space="preserve">JC Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J188">
+        <is>
           <t xml:space="preserve">Parsippany Super Kings</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I188">
-        <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J188">
-        <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8663,7 @@
       </c>
       <c t="inlineStr" r="E189">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F189">
@@ -8703,22 +8673,22 @@
       </c>
       <c t="inlineStr" r="G189">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H189">
         <is>
+          <t xml:space="preserve">Saffron Sapphire</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I189">
+        <is>
+          <t xml:space="preserve">Monroe Mavericks</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J189">
+        <is>
           <t xml:space="preserve">PCA Jr.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I189">
-        <is>
-          <t xml:space="preserve">PCA Jr.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J189">
-        <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -8738,32 +8708,27 @@
       </c>
       <c t="inlineStr" r="E190">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F190">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G190">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H190">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I190">
         <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J190">
-        <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8748,7 @@
       </c>
       <c t="inlineStr" r="E191">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F191">
@@ -8793,22 +8758,22 @@
       </c>
       <c t="inlineStr" r="G191">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H191">
         <is>
+          <t xml:space="preserve">Mystery Squad</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I191">
+        <is>
+          <t xml:space="preserve">Princeton Walk</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J191">
+        <is>
           <t xml:space="preserve">Cricket Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I191">
-        <is>
-          <t xml:space="preserve">Cricket Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J191">
-        <is>
-          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8793,7 @@
       </c>
       <c t="inlineStr" r="E192">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F192">
@@ -8838,22 +8803,17 @@
       </c>
       <c t="inlineStr" r="G192">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H192">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I192">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J192">
-        <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8833,7 @@
       </c>
       <c t="inlineStr" r="E193">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F193">
@@ -8883,22 +8843,22 @@
       </c>
       <c t="inlineStr" r="G193">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H193">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I193">
         <is>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J193">
+        <is>
           <t xml:space="preserve">Lincoln XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J193">
-        <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8878,7 @@
       </c>
       <c t="inlineStr" r="E194">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F194">
@@ -8928,22 +8888,17 @@
       </c>
       <c t="inlineStr" r="G194">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H194">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I194">
         <is>
-          <t xml:space="preserve">Raptors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J194">
-        <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8918,7 @@
       </c>
       <c t="inlineStr" r="E195">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F195">
@@ -8973,22 +8928,22 @@
       </c>
       <c t="inlineStr" r="G195">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H195">
         <is>
+          <t xml:space="preserve">Jersey City Dominators</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I195">
+        <is>
+          <t xml:space="preserve">VRK Gladiators</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J195">
+        <is>
           <t xml:space="preserve">Brown Munde</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I195">
-        <is>
-          <t xml:space="preserve">Brown Munde</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J195">
-        <is>
-          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -9008,7 +8963,7 @@
       </c>
       <c t="inlineStr" r="E196">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F196">
@@ -9018,22 +8973,22 @@
       </c>
       <c t="inlineStr" r="G196">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H196">
         <is>
+          <t xml:space="preserve">NJ Titans</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I196">
+        <is>
+          <t xml:space="preserve">Edison Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J196">
+        <is>
           <t xml:space="preserve">Trident CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I196">
-        <is>
-          <t xml:space="preserve">Trident CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J196">
-        <is>
-          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9008,7 @@
       </c>
       <c t="inlineStr" r="E197">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F197">
@@ -9063,22 +9018,22 @@
       </c>
       <c t="inlineStr" r="G197">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H197">
         <is>
+          <t xml:space="preserve">BLOODLINE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I197">
+        <is>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J197">
+        <is>
           <t xml:space="preserve">Waterfront Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I197">
-        <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J197">
-        <is>
-          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9053,7 @@
       </c>
       <c t="inlineStr" r="E198">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F198">
@@ -9108,22 +9063,17 @@
       </c>
       <c t="inlineStr" r="G198">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H198">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I198">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J198">
-        <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9093,7 @@
       </c>
       <c t="inlineStr" r="E199">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F199">
@@ -9153,22 +9103,22 @@
       </c>
       <c t="inlineStr" r="G199">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H199">
         <is>
+          <t xml:space="preserve">Power Hitters</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I199">
+        <is>
+          <t xml:space="preserve">Karma XI</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J199">
+        <is>
           <t xml:space="preserve">Nj Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I199">
-        <is>
-          <t xml:space="preserve">NJ Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J199">
-        <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9138,7 @@
       </c>
       <c t="inlineStr" r="E200">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F200">
@@ -9198,22 +9148,17 @@
       </c>
       <c t="inlineStr" r="G200">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H200">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I200">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J200">
-        <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9178,7 @@
       </c>
       <c t="inlineStr" r="E201">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F201">
@@ -9243,22 +9188,17 @@
       </c>
       <c t="inlineStr" r="G201">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H201">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I201">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J201">
-        <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9218,7 @@
       </c>
       <c t="inlineStr" r="E202">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/15/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F202">
@@ -9288,22 +9228,22 @@
       </c>
       <c t="inlineStr" r="G202">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H202">
         <is>
+          <t xml:space="preserve">CHAMPIONS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I202">
+        <is>
+          <t xml:space="preserve">RCW - Weekenders</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J202">
+        <is>
           <t xml:space="preserve">Windsor Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I202">
-        <is>
-          <t xml:space="preserve">Windsor Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J202">
-        <is>
-          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>

--- a/NJSBCL/data/weekenderscup_schedule.xlsx
+++ b/NJSBCL/data/weekenderscup_schedule.xlsx
@@ -323,7 +323,7 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F3">
@@ -333,22 +333,22 @@
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
     </row>
@@ -368,7 +368,7 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F4">
@@ -378,22 +378,22 @@
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve">Tridents XI</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F5">
@@ -423,22 +423,22 @@
       </c>
       <c t="inlineStr" r="G5">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
     </row>
@@ -458,7 +458,7 @@
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F6">
@@ -468,22 +468,22 @@
       </c>
       <c t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I6">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F7">
@@ -513,22 +513,22 @@
       </c>
       <c t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
@@ -558,22 +558,22 @@
       </c>
       <c t="inlineStr" r="G8">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F9">
@@ -603,17 +603,22 @@
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Edison Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J9">
+        <is>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
     </row>
@@ -633,7 +638,7 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
@@ -643,22 +648,22 @@
       </c>
       <c t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
     </row>
@@ -678,7 +683,7 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F11">
@@ -688,17 +693,22 @@
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">NJ Boxers</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J11">
+        <is>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
     </row>
@@ -718,27 +728,32 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G12">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J12">
+        <is>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
     </row>
@@ -758,7 +773,7 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
@@ -768,22 +783,22 @@
       </c>
       <c t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t xml:space="preserve">NJ Warriors</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
     </row>
@@ -803,7 +818,7 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
@@ -813,22 +828,22 @@
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
     </row>
@@ -848,7 +863,7 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F15">
@@ -858,22 +873,22 @@
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
     </row>
@@ -893,7 +908,7 @@
       </c>
       <c t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F16">
@@ -903,22 +918,22 @@
       </c>
       <c t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
     </row>
@@ -938,7 +953,7 @@
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F17">
@@ -948,22 +963,22 @@
       </c>
       <c t="inlineStr" r="G17">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I17">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -983,7 +998,7 @@
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F18">
@@ -993,22 +1008,22 @@
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I18">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">EM Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1043,7 @@
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
@@ -1038,22 +1053,22 @@
       </c>
       <c t="inlineStr" r="G19">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1088,7 @@
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F20">
@@ -1083,22 +1098,22 @@
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1133,7 @@
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F21">
@@ -1128,17 +1143,22 @@
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J21">
+        <is>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1178,7 @@
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">08/16/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F22">
@@ -1168,22 +1188,22 @@
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1223,7 @@
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
@@ -1218,17 +1238,17 @@
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1268,7 @@
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
@@ -1263,17 +1283,17 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">PMCC</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1313,7 @@
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
@@ -1308,17 +1328,17 @@
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1358,7 @@
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
@@ -1353,17 +1373,17 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1403,7 @@
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
@@ -1398,17 +1418,17 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1448,7 @@
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
@@ -1443,17 +1463,17 @@
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J28">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1493,7 @@
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
@@ -1488,17 +1508,17 @@
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="J29">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1538,7 @@
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
@@ -1533,17 +1553,17 @@
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J30">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1583,12 @@
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
@@ -1578,17 +1598,17 @@
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I31">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
       <c t="inlineStr" r="J31">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1628,7 @@
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
@@ -1623,17 +1643,17 @@
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Tridents XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J32">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1673,7 @@
       </c>
       <c t="inlineStr" r="E33">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F33">
@@ -1668,17 +1688,17 @@
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J33">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1718,7 @@
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
@@ -1713,17 +1733,17 @@
       </c>
       <c t="inlineStr" r="H34">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I34">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J34">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1763,7 @@
       </c>
       <c t="inlineStr" r="E35">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F35">
@@ -1758,17 +1778,17 @@
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I35">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J35">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1808,7 @@
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
@@ -1803,17 +1823,17 @@
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I36">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J36">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1853,7 @@
       </c>
       <c t="inlineStr" r="E37">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F37">
@@ -1848,17 +1868,17 @@
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I37">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J37">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1898,7 @@
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
@@ -1893,17 +1913,17 @@
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J38">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1943,7 @@
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
@@ -1938,17 +1958,17 @@
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J39">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1988,7 @@
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
@@ -1983,17 +2003,17 @@
       </c>
       <c t="inlineStr" r="H40">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I40">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J40">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2033,7 @@
       </c>
       <c t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F41">
@@ -2028,17 +2048,17 @@
       </c>
       <c t="inlineStr" r="H41">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I41">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J41">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2078,7 @@
       </c>
       <c t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">08/22/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F42">
@@ -2073,17 +2093,17 @@
       </c>
       <c t="inlineStr" r="H42">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I42">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J42">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2123,7 @@
       </c>
       <c t="inlineStr" r="E43">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F43">
@@ -2113,22 +2133,22 @@
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2168,7 @@
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
@@ -2158,22 +2178,22 @@
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I44">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">PMCC</t>
         </is>
       </c>
       <c t="inlineStr" r="J44">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2213,7 @@
       </c>
       <c t="inlineStr" r="E45">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F45">
@@ -2203,22 +2223,22 @@
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="J45">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2258,7 @@
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
@@ -2248,22 +2268,22 @@
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2303,7 @@
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
@@ -2293,22 +2313,22 @@
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I47">
         <is>
-          <t xml:space="preserve">Bloodline</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J47">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2348,7 @@
       </c>
       <c t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F48">
@@ -2338,22 +2358,22 @@
       </c>
       <c t="inlineStr" r="G48">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H48">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I48">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="J48">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2393,7 @@
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
@@ -2383,22 +2403,22 @@
       </c>
       <c t="inlineStr" r="G49">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J49">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2438,7 @@
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
@@ -2428,22 +2448,22 @@
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="J50">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2483,7 @@
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
@@ -2473,22 +2493,22 @@
       </c>
       <c t="inlineStr" r="G51">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
         <is>
-          <t xml:space="preserve">JC Mavericks</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="J51">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2528,7 @@
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
@@ -2518,22 +2538,22 @@
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t xml:space="preserve">Champions</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="J52">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2573,7 @@
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
@@ -2563,22 +2583,22 @@
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I53">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="J53">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2618,7 @@
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
@@ -2608,22 +2628,22 @@
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J54">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2663,7 @@
       </c>
       <c t="inlineStr" r="E55">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F55">
@@ -2653,22 +2673,22 @@
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="J55">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2708,7 @@
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
@@ -2698,22 +2718,22 @@
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="J56">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2753,7 @@
       </c>
       <c t="inlineStr" r="E57">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F57">
@@ -2743,22 +2763,22 @@
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J57">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2798,7 @@
       </c>
       <c t="inlineStr" r="E58">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F58">
@@ -2788,22 +2808,22 @@
       </c>
       <c t="inlineStr" r="G58">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H58">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="J58">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2843,7 @@
       </c>
       <c t="inlineStr" r="E59">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F59">
@@ -2833,22 +2853,22 @@
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="J59">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2888,7 @@
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
@@ -2878,22 +2898,22 @@
       </c>
       <c t="inlineStr" r="G60">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="J60">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2933,7 @@
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
@@ -2923,22 +2943,22 @@
       </c>
       <c t="inlineStr" r="G61">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
         <is>
-          <t xml:space="preserve">Jersey Tigers</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="J61">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2978,7 @@
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t xml:space="preserve">08/23/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
@@ -2968,22 +2988,22 @@
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="J62">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3023,7 @@
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
@@ -3018,17 +3038,17 @@
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="J63">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3068,7 @@
       </c>
       <c t="inlineStr" r="E64">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F64">
@@ -3063,17 +3083,17 @@
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J64">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3113,7 @@
       </c>
       <c t="inlineStr" r="E65">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F65">
@@ -3108,17 +3128,17 @@
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Bloodline</t>
         </is>
       </c>
       <c t="inlineStr" r="J65">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3158,7 @@
       </c>
       <c t="inlineStr" r="E66">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F66">
@@ -3153,17 +3173,17 @@
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J66">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3203,7 @@
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
@@ -3198,17 +3218,17 @@
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="J67">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3248,7 @@
       </c>
       <c t="inlineStr" r="E68">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F68">
@@ -3243,17 +3263,17 @@
       </c>
       <c t="inlineStr" r="H68">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I68">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="J68">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3293,7 @@
       </c>
       <c t="inlineStr" r="E69">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F69">
@@ -3288,17 +3308,17 @@
       </c>
       <c t="inlineStr" r="H69">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">JC Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J69">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3338,7 @@
       </c>
       <c t="inlineStr" r="E70">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F70">
@@ -3333,17 +3353,17 @@
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Champions</t>
         </is>
       </c>
       <c t="inlineStr" r="J70">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3383,7 @@
       </c>
       <c t="inlineStr" r="E71">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F71">
@@ -3378,17 +3398,17 @@
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J71">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3428,7 @@
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
@@ -3423,17 +3443,17 @@
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="J72">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3473,7 @@
       </c>
       <c t="inlineStr" r="E73">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F73">
@@ -3468,17 +3488,17 @@
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="J73">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3518,7 @@
       </c>
       <c t="inlineStr" r="E74">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F74">
@@ -3513,17 +3533,17 @@
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="J74">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3563,7 @@
       </c>
       <c t="inlineStr" r="E75">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F75">
@@ -3558,17 +3578,17 @@
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J75">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3608,7 @@
       </c>
       <c t="inlineStr" r="E76">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F76">
@@ -3603,17 +3623,17 @@
       </c>
       <c t="inlineStr" r="H76">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I76">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="J76">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3653,7 @@
       </c>
       <c t="inlineStr" r="E77">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F77">
@@ -3648,17 +3668,17 @@
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I77">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J77">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3698,7 @@
       </c>
       <c t="inlineStr" r="E78">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F78">
@@ -3693,17 +3713,17 @@
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I78">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J78">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3743,7 @@
       </c>
       <c t="inlineStr" r="E79">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F79">
@@ -3738,17 +3758,17 @@
       </c>
       <c t="inlineStr" r="H79">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I79">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J79">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3788,7 @@
       </c>
       <c t="inlineStr" r="E80">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F80">
@@ -3783,17 +3803,17 @@
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I80">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Jersey Tigers</t>
         </is>
       </c>
       <c t="inlineStr" r="J80">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3833,7 @@
       </c>
       <c t="inlineStr" r="E81">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F81">
@@ -3828,17 +3848,17 @@
       </c>
       <c t="inlineStr" r="H81">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I81">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J81">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3878,7 @@
       </c>
       <c t="inlineStr" r="E82">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F82">
@@ -3873,17 +3893,17 @@
       </c>
       <c t="inlineStr" r="H82">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I82">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="J82">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3923,7 @@
       </c>
       <c t="inlineStr" r="E83">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F83">
@@ -3913,22 +3933,22 @@
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I83">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J83">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3968,7 @@
       </c>
       <c t="inlineStr" r="E84">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F84">
@@ -3958,22 +3978,22 @@
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I84">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J84">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4013,7 @@
       </c>
       <c t="inlineStr" r="E85">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F85">
@@ -4003,22 +4023,22 @@
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I85">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="J85">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4058,7 @@
       </c>
       <c t="inlineStr" r="E86">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F86">
@@ -4048,22 +4068,22 @@
       </c>
       <c t="inlineStr" r="G86">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I86">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J86">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4103,7 @@
       </c>
       <c t="inlineStr" r="E87">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F87">
@@ -4093,22 +4113,22 @@
       </c>
       <c t="inlineStr" r="G87">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H87">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I87">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="J87">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4148,7 @@
       </c>
       <c t="inlineStr" r="E88">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F88">
@@ -4138,22 +4158,22 @@
       </c>
       <c t="inlineStr" r="G88">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H88">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I88">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J88">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4193,7 @@
       </c>
       <c t="inlineStr" r="E89">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F89">
@@ -4183,22 +4203,22 @@
       </c>
       <c t="inlineStr" r="G89">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H89">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I89">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J89">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4238,7 @@
       </c>
       <c t="inlineStr" r="E90">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F90">
@@ -4228,22 +4248,22 @@
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I90">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="J90">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
     </row>
@@ -4263,32 +4283,32 @@
       </c>
       <c t="inlineStr" r="E91">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G91">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H91">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I91">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="J91">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4328,7 @@
       </c>
       <c t="inlineStr" r="E92">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F92">
@@ -4318,22 +4338,22 @@
       </c>
       <c t="inlineStr" r="G92">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H92">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I92">
         <is>
-          <t xml:space="preserve">Tridents XI</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J92">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4373,7 @@
       </c>
       <c t="inlineStr" r="E93">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F93">
@@ -4363,22 +4383,22 @@
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I93">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="J93">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4418,7 @@
       </c>
       <c t="inlineStr" r="E94">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F94">
@@ -4408,22 +4428,22 @@
       </c>
       <c t="inlineStr" r="G94">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H94">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I94">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="J94">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4463,7 @@
       </c>
       <c t="inlineStr" r="E95">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F95">
@@ -4453,22 +4473,22 @@
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I95">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="J95">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4508,7 @@
       </c>
       <c t="inlineStr" r="E96">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F96">
@@ -4498,22 +4518,22 @@
       </c>
       <c t="inlineStr" r="G96">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H96">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I96">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J96">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4553,7 @@
       </c>
       <c t="inlineStr" r="E97">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F97">
@@ -4543,22 +4563,22 @@
       </c>
       <c t="inlineStr" r="G97">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H97">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I97">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J97">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4598,7 @@
       </c>
       <c t="inlineStr" r="E98">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F98">
@@ -4588,22 +4608,22 @@
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I98">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">EM Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J98">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4643,7 @@
       </c>
       <c t="inlineStr" r="E99">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F99">
@@ -4633,22 +4653,22 @@
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I99">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J99">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4688,7 @@
       </c>
       <c t="inlineStr" r="E100">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F100">
@@ -4678,22 +4698,22 @@
       </c>
       <c t="inlineStr" r="G100">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H100">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I100">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J100">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4733,7 @@
       </c>
       <c t="inlineStr" r="E101">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F101">
@@ -4723,22 +4743,22 @@
       </c>
       <c t="inlineStr" r="G101">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H101">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I101">
         <is>
-          <t xml:space="preserve">NJ Warriors</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J101">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4778,7 @@
       </c>
       <c t="inlineStr" r="E102">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F102">
@@ -4768,22 +4788,22 @@
       </c>
       <c t="inlineStr" r="G102">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H102">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I102">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="J102">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4823,7 @@
       </c>
       <c t="inlineStr" r="E103">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F103">
@@ -4818,17 +4838,17 @@
       </c>
       <c t="inlineStr" r="H103">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I103">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J103">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4868,7 @@
       </c>
       <c t="inlineStr" r="E104">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F104">
@@ -4863,17 +4883,17 @@
       </c>
       <c t="inlineStr" r="H104">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I104">
         <is>
-          <t xml:space="preserve">PMCC</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J104">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4913,7 @@
       </c>
       <c t="inlineStr" r="E105">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F105">
@@ -4908,17 +4928,17 @@
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I105">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J105">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4958,7 @@
       </c>
       <c t="inlineStr" r="E106">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F106">
@@ -4953,17 +4973,17 @@
       </c>
       <c t="inlineStr" r="H106">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I106">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J106">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5003,7 @@
       </c>
       <c t="inlineStr" r="E107">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F107">
@@ -4998,17 +5018,17 @@
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I107">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="J107">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5048,7 @@
       </c>
       <c t="inlineStr" r="E108">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F108">
@@ -5043,17 +5063,17 @@
       </c>
       <c t="inlineStr" r="H108">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I108">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J108">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5093,7 @@
       </c>
       <c t="inlineStr" r="E109">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F109">
@@ -5088,17 +5108,17 @@
       </c>
       <c t="inlineStr" r="H109">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I109">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="J109">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -5118,12 +5138,12 @@
       </c>
       <c t="inlineStr" r="E110">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G110">
@@ -5133,17 +5153,17 @@
       </c>
       <c t="inlineStr" r="H110">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I110">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
       <c t="inlineStr" r="J110">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5183,7 @@
       </c>
       <c t="inlineStr" r="E111">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F111">
@@ -5178,17 +5198,17 @@
       </c>
       <c t="inlineStr" r="H111">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I111">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J111">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5228,7 @@
       </c>
       <c t="inlineStr" r="E112">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F112">
@@ -5223,17 +5243,17 @@
       </c>
       <c t="inlineStr" r="H112">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I112">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J112">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5273,7 @@
       </c>
       <c t="inlineStr" r="E113">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F113">
@@ -5268,17 +5288,17 @@
       </c>
       <c t="inlineStr" r="H113">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I113">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J113">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5318,7 @@
       </c>
       <c t="inlineStr" r="E114">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F114">
@@ -5313,17 +5333,17 @@
       </c>
       <c t="inlineStr" r="H114">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I114">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J114">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5363,7 @@
       </c>
       <c t="inlineStr" r="E115">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F115">
@@ -5358,17 +5378,17 @@
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I115">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J115">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5408,7 @@
       </c>
       <c t="inlineStr" r="E116">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F116">
@@ -5403,17 +5423,17 @@
       </c>
       <c t="inlineStr" r="H116">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I116">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J116">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5453,7 @@
       </c>
       <c t="inlineStr" r="E117">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F117">
@@ -5448,17 +5468,17 @@
       </c>
       <c t="inlineStr" r="H117">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I117">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J117">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5498,7 @@
       </c>
       <c t="inlineStr" r="E118">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F118">
@@ -5493,17 +5513,17 @@
       </c>
       <c t="inlineStr" r="H118">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I118">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J118">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5543,7 @@
       </c>
       <c t="inlineStr" r="E119">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F119">
@@ -5538,17 +5558,17 @@
       </c>
       <c t="inlineStr" r="H119">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I119">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J119">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5588,7 @@
       </c>
       <c t="inlineStr" r="E120">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F120">
@@ -5583,17 +5603,17 @@
       </c>
       <c t="inlineStr" r="H120">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I120">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J120">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5633,7 @@
       </c>
       <c t="inlineStr" r="E121">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F121">
@@ -5628,17 +5648,17 @@
       </c>
       <c t="inlineStr" r="H121">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I121">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J121">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5678,7 @@
       </c>
       <c t="inlineStr" r="E122">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F122">
@@ -5673,17 +5693,17 @@
       </c>
       <c t="inlineStr" r="H122">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I122">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J122">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5723,7 @@
       </c>
       <c t="inlineStr" r="E123">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F123">
@@ -5713,22 +5733,22 @@
       </c>
       <c t="inlineStr" r="G123">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H123">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I123">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J123">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5768,7 @@
       </c>
       <c t="inlineStr" r="E124">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F124">
@@ -5758,22 +5778,22 @@
       </c>
       <c t="inlineStr" r="G124">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H124">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I124">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Jersey Tigers</t>
         </is>
       </c>
       <c t="inlineStr" r="J124">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5813,7 @@
       </c>
       <c t="inlineStr" r="E125">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F125">
@@ -5803,22 +5823,22 @@
       </c>
       <c t="inlineStr" r="G125">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H125">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I125">
         <is>
-          <t xml:space="preserve">Bloodline</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J125">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5858,7 @@
       </c>
       <c t="inlineStr" r="E126">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F126">
@@ -5848,22 +5868,22 @@
       </c>
       <c t="inlineStr" r="G126">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H126">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I126">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J126">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5903,7 @@
       </c>
       <c t="inlineStr" r="E127">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F127">
@@ -5893,22 +5913,22 @@
       </c>
       <c t="inlineStr" r="G127">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H127">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I127">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="J127">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5948,7 @@
       </c>
       <c t="inlineStr" r="E128">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F128">
@@ -5938,22 +5958,22 @@
       </c>
       <c t="inlineStr" r="G128">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H128">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I128">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J128">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5993,7 @@
       </c>
       <c t="inlineStr" r="E129">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F129">
@@ -5983,22 +6003,22 @@
       </c>
       <c t="inlineStr" r="G129">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H129">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I129">
         <is>
-          <t xml:space="preserve">JC Mavericks</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="J129">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6038,7 @@
       </c>
       <c t="inlineStr" r="E130">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F130">
@@ -6028,22 +6048,22 @@
       </c>
       <c t="inlineStr" r="G130">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H130">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I130">
         <is>
-          <t xml:space="preserve">Champions</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="J130">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6083,7 @@
       </c>
       <c t="inlineStr" r="E131">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F131">
@@ -6073,22 +6093,22 @@
       </c>
       <c t="inlineStr" r="G131">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H131">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I131">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J131">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6128,7 @@
       </c>
       <c t="inlineStr" r="E132">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F132">
@@ -6118,22 +6138,22 @@
       </c>
       <c t="inlineStr" r="G132">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H132">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I132">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="J132">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6173,7 @@
       </c>
       <c t="inlineStr" r="E133">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F133">
@@ -6163,22 +6183,22 @@
       </c>
       <c t="inlineStr" r="G133">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H133">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I133">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Champions</t>
         </is>
       </c>
       <c t="inlineStr" r="J133">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6218,7 @@
       </c>
       <c t="inlineStr" r="E134">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F134">
@@ -6208,22 +6228,22 @@
       </c>
       <c t="inlineStr" r="G134">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H134">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I134">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">JC Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J134">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6263,7 @@
       </c>
       <c t="inlineStr" r="E135">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F135">
@@ -6253,22 +6273,22 @@
       </c>
       <c t="inlineStr" r="G135">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H135">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I135">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="J135">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6308,7 @@
       </c>
       <c t="inlineStr" r="E136">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F136">
@@ -6298,22 +6318,22 @@
       </c>
       <c t="inlineStr" r="G136">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H136">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I136">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="J136">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6353,7 @@
       </c>
       <c t="inlineStr" r="E137">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F137">
@@ -6343,22 +6363,17 @@
       </c>
       <c t="inlineStr" r="G137">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H137">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I137">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J137">
-        <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6393,7 @@
       </c>
       <c t="inlineStr" r="E138">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F138">
@@ -6388,22 +6403,17 @@
       </c>
       <c t="inlineStr" r="G138">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H138">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I138">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J138">
-        <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Bloodline</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6433,7 @@
       </c>
       <c t="inlineStr" r="E139">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F139">
@@ -6433,22 +6443,22 @@
       </c>
       <c t="inlineStr" r="G139">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H139">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I139">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J139">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6478,7 @@
       </c>
       <c t="inlineStr" r="E140">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F140">
@@ -6478,22 +6488,22 @@
       </c>
       <c t="inlineStr" r="G140">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H140">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I140">
         <is>
-          <t xml:space="preserve">Jersey Tigers</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="J140">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6523,7 @@
       </c>
       <c t="inlineStr" r="E141">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F141">
@@ -6523,22 +6533,22 @@
       </c>
       <c t="inlineStr" r="G141">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H141">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I141">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="J141">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6568,7 @@
       </c>
       <c t="inlineStr" r="E142">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">08/23/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F142">
@@ -6568,22 +6578,22 @@
       </c>
       <c t="inlineStr" r="G142">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H142">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I142">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J142">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6613,7 @@
       </c>
       <c t="inlineStr" r="E143">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F143">
@@ -6613,22 +6623,22 @@
       </c>
       <c t="inlineStr" r="G143">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H143">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I143">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="J143">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6658,7 @@
       </c>
       <c t="inlineStr" r="E144">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F144">
@@ -6658,22 +6668,22 @@
       </c>
       <c t="inlineStr" r="G144">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H144">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I144">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="J144">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6703,7 @@
       </c>
       <c t="inlineStr" r="E145">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F145">
@@ -6703,22 +6713,22 @@
       </c>
       <c t="inlineStr" r="G145">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H145">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I145">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="J145">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6748,7 @@
       </c>
       <c t="inlineStr" r="E146">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F146">
@@ -6748,22 +6758,22 @@
       </c>
       <c t="inlineStr" r="G146">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H146">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I146">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="J146">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6793,7 @@
       </c>
       <c t="inlineStr" r="E147">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F147">
@@ -6793,22 +6803,22 @@
       </c>
       <c t="inlineStr" r="G147">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H147">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I147">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="J147">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6838,7 @@
       </c>
       <c t="inlineStr" r="E148">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F148">
@@ -6838,22 +6848,22 @@
       </c>
       <c t="inlineStr" r="G148">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H148">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I148">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J148">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6883,7 @@
       </c>
       <c t="inlineStr" r="E149">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F149">
@@ -6883,22 +6893,22 @@
       </c>
       <c t="inlineStr" r="G149">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H149">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I149">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="J149">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6928,7 @@
       </c>
       <c t="inlineStr" r="E150">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F150">
@@ -6928,22 +6938,22 @@
       </c>
       <c t="inlineStr" r="G150">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H150">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I150">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="J150">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6973,7 @@
       </c>
       <c t="inlineStr" r="E151">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F151">
@@ -6973,22 +6983,22 @@
       </c>
       <c t="inlineStr" r="G151">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H151">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I151">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J151">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7018,7 @@
       </c>
       <c t="inlineStr" r="E152">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F152">
@@ -7018,22 +7028,22 @@
       </c>
       <c t="inlineStr" r="G152">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H152">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I152">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="J152">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7063,7 @@
       </c>
       <c t="inlineStr" r="E153">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F153">
@@ -7063,22 +7073,22 @@
       </c>
       <c t="inlineStr" r="G153">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H153">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I153">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="J153">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7108,7 @@
       </c>
       <c t="inlineStr" r="E154">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F154">
@@ -7108,22 +7118,22 @@
       </c>
       <c t="inlineStr" r="G154">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H154">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I154">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="J154">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7153,7 @@
       </c>
       <c t="inlineStr" r="E155">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F155">
@@ -7153,22 +7163,22 @@
       </c>
       <c t="inlineStr" r="G155">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H155">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I155">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="J155">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7198,7 @@
       </c>
       <c t="inlineStr" r="E156">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F156">
@@ -7198,22 +7208,22 @@
       </c>
       <c t="inlineStr" r="G156">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H156">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I156">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J156">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7243,7 @@
       </c>
       <c t="inlineStr" r="E157">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F157">
@@ -7243,22 +7253,17 @@
       </c>
       <c t="inlineStr" r="G157">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H157">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I157">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J157">
-        <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7283,7 @@
       </c>
       <c t="inlineStr" r="E158">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F158">
@@ -7288,22 +7293,22 @@
       </c>
       <c t="inlineStr" r="G158">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H158">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I158">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J158">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7328,7 @@
       </c>
       <c t="inlineStr" r="E159">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F159">
@@ -7333,22 +7338,22 @@
       </c>
       <c t="inlineStr" r="G159">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H159">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I159">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J159">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7373,7 @@
       </c>
       <c t="inlineStr" r="E160">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F160">
@@ -7378,22 +7383,22 @@
       </c>
       <c t="inlineStr" r="G160">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H160">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I160">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="J160">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7418,7 @@
       </c>
       <c t="inlineStr" r="E161">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F161">
@@ -7423,22 +7428,22 @@
       </c>
       <c t="inlineStr" r="G161">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H161">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I161">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">PMCC</t>
         </is>
       </c>
       <c t="inlineStr" r="J161">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7463,7 @@
       </c>
       <c t="inlineStr" r="E162">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/22/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F162">
@@ -7468,22 +7473,22 @@
       </c>
       <c t="inlineStr" r="G162">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H162">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I162">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J162">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7508,7 @@
       </c>
       <c t="inlineStr" r="E163">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F163">
@@ -7513,22 +7518,22 @@
       </c>
       <c t="inlineStr" r="G163">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H163">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I163">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J163">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7553,7 @@
       </c>
       <c t="inlineStr" r="E164">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F164">
@@ -7558,22 +7563,17 @@
       </c>
       <c t="inlineStr" r="G164">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H164">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I164">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J164">
-        <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c t="inlineStr" r="E165">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F165">
@@ -7603,22 +7603,22 @@
       </c>
       <c t="inlineStr" r="G165">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H165">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I165">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J165">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c t="inlineStr" r="E166">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F166">
@@ -7648,22 +7648,22 @@
       </c>
       <c t="inlineStr" r="G166">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H166">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I166">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J166">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       </c>
       <c t="inlineStr" r="E167">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F167">
@@ -7693,22 +7693,22 @@
       </c>
       <c t="inlineStr" r="G167">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H167">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I167">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J167">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c t="inlineStr" r="E168">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F168">
@@ -7738,22 +7738,22 @@
       </c>
       <c t="inlineStr" r="G168">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H168">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I168">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J168">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c t="inlineStr" r="E169">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F169">
@@ -7783,22 +7783,22 @@
       </c>
       <c t="inlineStr" r="G169">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H169">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I169">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J169">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -7818,32 +7818,32 @@
       </c>
       <c t="inlineStr" r="E170">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G170">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H170">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I170">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J170">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c t="inlineStr" r="E171">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F171">
@@ -7873,22 +7873,22 @@
       </c>
       <c t="inlineStr" r="G171">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H171">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I171">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J171">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c t="inlineStr" r="E172">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F172">
@@ -7918,22 +7918,22 @@
       </c>
       <c t="inlineStr" r="G172">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H172">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I172">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J172">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -7953,32 +7953,27 @@
       </c>
       <c t="inlineStr" r="E173">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F173">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G173">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H173">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I173">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J173">
-        <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7993,7 @@
       </c>
       <c t="inlineStr" r="E174">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F174">
@@ -8008,22 +8003,17 @@
       </c>
       <c t="inlineStr" r="G174">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H174">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I174">
         <is>
-          <t xml:space="preserve">Raptors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J174">
-        <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8033,7 @@
       </c>
       <c t="inlineStr" r="E175">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F175">
@@ -8053,22 +8043,22 @@
       </c>
       <c t="inlineStr" r="G175">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H175">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I175">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J175">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8078,7 @@
       </c>
       <c t="inlineStr" r="E176">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F176">
@@ -8098,22 +8088,17 @@
       </c>
       <c t="inlineStr" r="G176">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H176">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I176">
         <is>
-          <t xml:space="preserve">Trident CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J176">
-        <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8118,7 @@
       </c>
       <c t="inlineStr" r="E177">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F177">
@@ -8143,22 +8128,22 @@
       </c>
       <c t="inlineStr" r="G177">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H177">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I177">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J177">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8163,7 @@
       </c>
       <c t="inlineStr" r="E178">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F178">
@@ -8188,22 +8173,22 @@
       </c>
       <c t="inlineStr" r="G178">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H178">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I178">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J178">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8208,7 @@
       </c>
       <c t="inlineStr" r="E179">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F179">
@@ -8233,22 +8218,22 @@
       </c>
       <c t="inlineStr" r="G179">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H179">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I179">
         <is>
-          <t xml:space="preserve">NJ Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J179">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8253,7 @@
       </c>
       <c t="inlineStr" r="E180">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F180">
@@ -8278,22 +8263,22 @@
       </c>
       <c t="inlineStr" r="G180">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H180">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I180">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J180">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8298,7 @@
       </c>
       <c t="inlineStr" r="E181">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F181">
@@ -8323,22 +8308,22 @@
       </c>
       <c t="inlineStr" r="G181">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H181">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I181">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Tridents XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J181">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8343,7 @@
       </c>
       <c t="inlineStr" r="E182">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/16/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F182">
@@ -8368,22 +8353,22 @@
       </c>
       <c t="inlineStr" r="G182">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H182">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I182">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="J182">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>

--- a/NJSBCL/data/weekenderscup_schedule.xlsx
+++ b/NJSBCL/data/weekenderscup_schedule.xlsx
@@ -661,11 +661,6 @@
           <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
-      <c t="inlineStr" r="J10">
-        <is>
-          <t xml:space="preserve">Raptors</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="65">
